--- a/recruiter_forms/001_responsive_interview_questionnaire_form--recruiter_forms.xlsx
+++ b/recruiter_forms/001_responsive_interview_questionnaire_form--recruiter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'undecided',_'value':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Undecided', 'value': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'freelancer',_'value':_'freelancer'}</t>
+          <t>freelancer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Freelancer', 'value': 'Freelancer'}</t>
+          <t>Freelancer</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Full-time', 'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive',_'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive', 'value': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Neutral', 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'negative',_'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Negative', 'value': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'15_minutes',_'value':_'15_minutes'}</t>
+          <t>15_minutes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '15 minutes', 'value': '15 minutes'}</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'30_minutes',_'value':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '30 minutes', 'value': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'60_minutes',_'value':_'60_minutes'}</t>
+          <t>60_minutes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '60 minutes', 'value': '60 minutes'}</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'1_hour',_'value':_'1_hour'}</t>
+          <t>1_hour</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '1 hour', 'value': '1 hour'}</t>
+          <t>1 hour</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit',_'value':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit', 'value': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'save_as_draft',_'value':_'save_as_draft'}</t>
+          <t>save_as_draft</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Save as draft', 'value': 'Save as draft'}</t>
+          <t>Save as draft</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bad',_'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bad', 'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'social_media',_'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Social media', 'value': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'google_search',_'value':_'google_search'}</t>
+          <t>google_search</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Google search', 'value': 'Google search'}</t>
+          <t>Google search</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'referral',_'value':_'referral'}</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Referral', 'value': 'Referral'}</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
